--- a/KEEN 30m Subtidal Example/GOOS_EOV_Species_List.xlsx
+++ b/KEEN 30m Subtidal Example/GOOS_EOV_Species_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jebyrnes/Library/CloudStorage/GoogleDrive-jarrett.byrnes@gmail.com/.shortcut-targets-by-id/1uNfJ83WmlmCErHo4iUjWr1UYx8ZEmsih/Macroalgal EOV Data Processing docs/SOP_Visual/goos_data_sheets_and_entry_forms/KEEN 30m Subtidal Example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953839E3-BBE5-524D-B0AE-59313569FAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20932016-212C-974B-B3FC-03BEBCE1381C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="172">
   <si>
     <t>Species Code</t>
   </si>
@@ -536,17 +536,30 @@
   </si>
   <si>
     <t>CATAMI Version</t>
+  </si>
+  <si>
+    <t>Essential Ocean Variable</t>
+  </si>
+  <si>
+    <t>Macroalgal Canopy Cover and Composition</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -617,6 +630,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -638,46 +659,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
@@ -906,7 +929,7 @@
     <col min="9" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -931,8 +954,11 @@
       <c r="H1" s="18" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I1" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -957,8 +983,11 @@
       <c r="H2" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I2" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
@@ -984,7 +1013,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -1010,7 +1039,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -1036,7 +1065,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
@@ -1061,8 +1090,11 @@
       <c r="H6" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
@@ -1087,8 +1119,11 @@
       <c r="H7" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I7" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>25</v>
       </c>
@@ -1113,8 +1148,11 @@
       <c r="H8" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
@@ -1139,8 +1177,11 @@
       <c r="H9" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
@@ -1166,7 +1207,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>32</v>
       </c>
@@ -1191,8 +1232,11 @@
       <c r="H11" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I11" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>34</v>
       </c>
@@ -1218,7 +1262,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>36</v>
       </c>
@@ -1243,8 +1287,11 @@
       <c r="H13" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I13" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>38</v>
       </c>
@@ -1270,7 +1317,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>41</v>
       </c>
@@ -1296,7 +1343,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
@@ -1322,7 +1369,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -1348,7 +1395,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>49</v>
       </c>
@@ -1374,7 +1421,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>52</v>
       </c>
@@ -1400,7 +1447,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>55</v>
       </c>
@@ -1425,8 +1472,11 @@
       <c r="H20" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>57</v>
       </c>
@@ -1451,8 +1501,11 @@
       <c r="H21" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I21" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>59</v>
       </c>
@@ -1477,8 +1530,11 @@
       <c r="H22" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I22" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>61</v>
       </c>
@@ -1503,8 +1559,11 @@
       <c r="H23" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>62</v>
       </c>
@@ -1529,8 +1588,11 @@
       <c r="H24" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I24" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>64</v>
       </c>
@@ -1555,8 +1617,11 @@
       <c r="H25" s="2">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I25" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
@@ -1582,7 +1647,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>67</v>
       </c>
@@ -1608,7 +1673,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>71</v>
       </c>
@@ -1634,7 +1699,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>74</v>
       </c>
@@ -1660,7 +1725,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>78</v>
       </c>
@@ -1686,7 +1751,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>81</v>
       </c>
@@ -1712,7 +1777,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>84</v>
       </c>
